--- a/US_3D_Design_Studios.xlsx
+++ b/US_3D_Design_Studios.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Design Studios'!$A$1:$L$116</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'3D Job Sites'!$A$1:$H$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'3D Job Sites'!$A$1:$H$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -52,7 +52,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -129,6 +129,11 @@
         <fgColor rgb="00F6F6EA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF7F7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -142,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -281,6 +286,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7865,7 +7882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9144,7 +9161,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>From other agent's list</t>
+          <t>From other agent's list (#1)</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9201,7 @@
       </c>
       <c r="H33" s="35" t="inlineStr">
         <is>
-          <t>From other agent's list</t>
+          <t>From other agent's list (#1)</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9241,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>From other agent's list</t>
+          <t>From other agent's list (#1)</t>
         </is>
       </c>
     </row>
@@ -9264,7 +9281,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>From other agent's list</t>
+          <t>From other agent's list (#1)</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9321,7 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>From other agent's list</t>
+          <t>From other agent's list (#1)</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9361,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>From other agent's list</t>
+          <t>From other agent's list (#1)</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9401,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>From other agent's list</t>
+          <t>From other agent's list (#1)</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9441,7 @@
       </c>
       <c r="H39" s="46" t="inlineStr">
         <is>
-          <t>From other agent's list</t>
+          <t>From other agent's list (#1)</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9481,7 @@
       </c>
       <c r="H40" s="46" t="inlineStr">
         <is>
-          <t>From other agent's list</t>
+          <t>From other agent's list (#1)</t>
         </is>
       </c>
     </row>
@@ -9504,7 +9521,7 @@
       </c>
       <c r="H41" s="49" t="inlineStr">
         <is>
-          <t>From other agent's list</t>
+          <t>From other agent's list (#1)</t>
         </is>
       </c>
     </row>
@@ -9540,7 +9557,7 @@
       </c>
       <c r="H42" s="49" t="inlineStr">
         <is>
-          <t>From other agent's list</t>
+          <t>From other agent's list (#1)</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9593,7 @@
       </c>
       <c r="H43" s="49" t="inlineStr">
         <is>
-          <t>From other agent's list</t>
+          <t>From other agent's list (#1)</t>
         </is>
       </c>
     </row>
@@ -9612,7 +9629,7 @@
       </c>
       <c r="H44" s="49" t="inlineStr">
         <is>
-          <t>From other agent's list</t>
+          <t>From other agent's list (#1)</t>
         </is>
       </c>
     </row>
@@ -9652,12 +9669,332 @@
       </c>
       <c r="H45" s="49" t="inlineStr">
         <is>
-          <t>From other agent's list</t>
+          <t>From other agent's list (#1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>PocketGamer.biz Jobs</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pocketgamer.jobs</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Mobile and cross-platform game studios</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Run by PocketGamer.biz. Lists 3D environment, prop and technical art roles.</t>
+        </is>
+      </c>
+      <c r="G46" s="52" t="inlineStr">
+        <is>
+          <t>Not checked — site blocks automated reading</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>From other agent's list (#2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>GameDevMap</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gamedevmap.com</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Finding game studios by location</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Not a job board — a map/directory of game studios. Use it to find studios near Seattle, then check their careers pages. Active (says ~100,000 users in 2025).</t>
+        </is>
+      </c>
+      <c r="G47" s="33" t="inlineStr">
+        <is>
+          <t>Yes — live, saw current jobs</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>From other agent's list (#2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>CGVerse Job Search</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>https://cgverse.com/jobs</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Concept, 3D and technical art roles</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Run by an online art school. Most listings are pulled from ArtStation, so expect overlap with ArtStation Jobs. Saw current roles from Crytek, Ubisoft and Visual Concepts.</t>
+        </is>
+      </c>
+      <c r="G48" s="33" t="inlineStr">
+        <is>
+          <t>Yes — live, saw current jobs</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>From other agent's list (#2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="21" t="inlineStr">
+        <is>
+          <t>CGTrader Jobs</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cgtrader.com/3d-modeling-jobs/browse</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Design agencies &amp; product</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Contract 3D modeling tasks</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>3D model marketplace with a job/project board. Page loaded, but listings didn't show.</t>
+        </is>
+      </c>
+      <c r="G49" s="34" t="inlineStr">
+        <is>
+          <t>Site loads, but I couldn't see listings</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>From other agent's list (#2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="53" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="54" t="inlineStr">
+        <is>
+          <t>Upwork</t>
+        </is>
+      </c>
+      <c r="C50" s="55" t="inlineStr">
+        <is>
+          <t>https://www.upwork.com</t>
+        </is>
+      </c>
+      <c r="D50" s="53" t="inlineStr">
+        <is>
+          <t>Freelance &amp; remote</t>
+        </is>
+      </c>
+      <c r="E50" s="53" t="inlineStr">
+        <is>
+          <t>Freelance 3D contracts</t>
+        </is>
+      </c>
+      <c r="F50" s="53" t="inlineStr">
+        <is>
+          <t>Lots of low-budget posts. Search specific terms like "Unreal environment", "product visualization", "WebGL 3D".</t>
+        </is>
+      </c>
+      <c r="G50" s="53" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
+      <c r="H50" s="53" t="inlineStr">
+        <is>
+          <t>From other agent's list (#2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="53" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="54" t="inlineStr">
+        <is>
+          <t>We Work Remotely</t>
+        </is>
+      </c>
+      <c r="C51" s="55" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com</t>
+        </is>
+      </c>
+      <c r="D51" s="53" t="inlineStr">
+        <is>
+          <t>Freelance &amp; remote</t>
+        </is>
+      </c>
+      <c r="E51" s="53" t="inlineStr">
+        <is>
+          <t>Remote design and 3D roles</t>
+        </is>
+      </c>
+      <c r="F51" s="53" t="inlineStr">
+        <is>
+          <t>Large remote board (42,000+ jobs posted). Has 3D Modeling and 3D Animation skill filters; saw a remote Senior 3D Designer contract role.</t>
+        </is>
+      </c>
+      <c r="G51" s="33" t="inlineStr">
+        <is>
+          <t>Yes — live, saw current jobs</t>
+        </is>
+      </c>
+      <c r="H51" s="53" t="inlineStr">
+        <is>
+          <t>From other agent's list (#2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="54" t="inlineStr">
+        <is>
+          <t>Remote Rocketship</t>
+        </is>
+      </c>
+      <c r="C52" s="55" t="inlineStr">
+        <is>
+          <t>https://www.remoterocketship.com</t>
+        </is>
+      </c>
+      <c r="D52" s="53" t="inlineStr">
+        <is>
+          <t>Freelance &amp; remote</t>
+        </is>
+      </c>
+      <c r="E52" s="53" t="inlineStr">
+        <is>
+          <t>Remote jobs pulled from company careers pages</t>
+        </is>
+      </c>
+      <c r="F52" s="53" t="inlineStr">
+        <is>
+          <t>Active. Use the Design filter and search "3D". Full search may need a free account.</t>
+        </is>
+      </c>
+      <c r="G52" s="33" t="inlineStr">
+        <is>
+          <t>Yes — live, saw current jobs</t>
+        </is>
+      </c>
+      <c r="H52" s="53" t="inlineStr">
+        <is>
+          <t>From other agent's list (#2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="54" t="inlineStr">
+        <is>
+          <t>Arc.dev</t>
+        </is>
+      </c>
+      <c r="C53" s="55" t="inlineStr">
+        <is>
+          <t>https://arc.dev/remote-jobs/3d-artist</t>
+        </is>
+      </c>
+      <c r="D53" s="53" t="inlineStr">
+        <is>
+          <t>Freelance &amp; remote</t>
+        </is>
+      </c>
+      <c r="E53" s="53" t="inlineStr">
+        <is>
+          <t>Technical / real-time 3D and WebGL roles</t>
+        </is>
+      </c>
+      <c r="F53" s="53" t="inlineStr">
+        <is>
+          <t>Mostly for developers. Its 3D Artist page had 0 jobs when checked.</t>
+        </is>
+      </c>
+      <c r="G53" s="34" t="inlineStr">
+        <is>
+          <t>Site loads, but I couldn't see listings</t>
+        </is>
+      </c>
+      <c r="H53" s="53" t="inlineStr">
+        <is>
+          <t>From other agent's list (#2)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H45"/>
+  <autoFilter ref="A1:H53"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -9702,6 +10039,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
